--- a/docs/要件定義_ELN_v1.0.xlsx
+++ b/docs/要件定義_ELN_v1.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-22.04\home\rde2\gitlab\RDE_ELN\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kawagishi-yuya\ELN_Local\rde-excel-eln\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768340E6-B9E3-485E-85E3-F7A7478E6C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB71EB2-D8B4-44FB-AA59-12196B340076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="要件定義（手入力 メタデータ項目リスト）_bak" sheetId="15" state="hidden" r:id="rId1"/>
@@ -74,6 +74,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -87,38 +96,20 @@
   <commentList>
     <comment ref="F26" authorId="0" shapeId="0" xr:uid="{8EC9289B-E89B-C54A-AF5E-A9CAB7783195}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Yu Gothic"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[スレッド化されたコメント]
+        <t>[スレッド化されたコメント]
 使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
 コメント:
     「スパイク除去/spike removal」などとするのが良いでしょう。（特異点除去という言葉は物理学上かなり特定の意味を持つ言葉で、今回の処理はそれに当たらないため）
 返信:
 OKです。</t>
-        </r>
       </text>
     </comment>
     <comment ref="F27" authorId="1" shapeId="0" xr:uid="{296B8175-6133-1340-B050-FB33F3C0CC15}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Yu Gothic"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[スレッド化されたコメント]
+        <t>[スレッド化されたコメント]
 使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
 コメント:
     「取得」というか、「特出し表示」？　取得でも良いですが、一応議論したく</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -136,15 +127,7 @@
   <commentList>
     <comment ref="L27" authorId="0" shapeId="0" xr:uid="{AD545E9C-6EAD-7444-868D-1DA9DDED3D54}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Yu Gothic"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[スレッド化されたコメント]
+        <t>[スレッド化されたコメント]
 使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
 コメント:
     数値型に固執させるなら、サンプル幅・サンプル長さ・サンプル厚さの3項目に分ける必要が出てきますか？
@@ -152,56 +135,29 @@
 はい、そう思います。DX的にそうするのか、現場の実情に合わせてこのようにするのか、コメント欄（SAMPLE_COMMENT）に特別なルールを設けてSAMPLE_SIZEやSAMPLE_VOLUMEに計算してマッピングするか、などが考えられると思います。
 送り状にこの3つの項目を持たせようと思っていますが、それとの関係も検討必要です。
 DXにこだわりすぎて、実情に合わないことをやっても仕方ないと思いますので悩みます。</t>
-        </r>
       </text>
     </comment>
     <comment ref="F36" authorId="1" shapeId="0" xr:uid="{14C21C5E-7A44-AA48-B84A-2B7A0F5A94D8}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Yu Gothic"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[スレッド化されたコメント]
+        <t>[スレッド化されたコメント]
 使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
 コメント:
     "coercivity" のようなちゃんとした英語名ではなく、記号を英語名扱いで格納するということでいいなら、これでOKです。この下のセルも同様
 返信:
 確かにそうですね。基本的に略語は使用しない、という原則で考えていますが、磁性分野では常識な語彙なのでOKと考えるか、ということですね。</t>
-        </r>
       </text>
     </comment>
     <comment ref="H37" authorId="2" shapeId="0" xr:uid="{C11FE378-AC52-5844-93E3-10FA1B4B2ECC}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Yu Gothic"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[スレッド化されたコメント]
+        <t>[スレッド化されたコメント]
 使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
 コメント:
     emuは標準単位系ではないので、高橋さん用途には良いとしても、汎用としては別の単位に換算すべきな気がする</t>
-        </r>
       </text>
     </comment>
     <comment ref="F39" authorId="3" shapeId="0" xr:uid="{EFCB1198-F542-704F-9335-CDD4A0F5BC07}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Yu Gothic"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[スレッド化されたコメント]
+        <t>[スレッド化されたコメント]
 使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
 コメント:
     Br per volume か？
@@ -221,7 +177,6 @@
 高橋さんのメタは
 「残留磁化x膜厚(memu):3.92e-03」
 となっており、残留磁化はBrを使用しています。整理必要かもしれません。</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -1560,6 +1515,13 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>川岸</t>
+    <rPh sb="0" eb="2">
+      <t>カワギシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>拡張子がxlsxであること</t>
     <rPh sb="0" eb="3">
       <t>カクチョウシ</t>
@@ -1766,10 +1728,6 @@
   </si>
   <si>
     <t>item</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>NIMS</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2983,7 +2941,28 @@
     <cellStyle name="標準 2" xfId="1" xr:uid="{40251804-E9E9-43A3-956E-E079063D14C4}"/>
     <cellStyle name="標準 4" xfId="2" xr:uid="{965AAE8D-7E1A-4798-B53C-4043C6350A54}"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC1C1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -4922,16 +4901,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{660A9BF0-6A59-4E51-B01C-7C6C93D7E843}">
   <dimension ref="A1:N50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="2" width="19" style="3" customWidth="1"/>
-    <col min="3" max="3" width="50.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="50.83203125" style="3" customWidth="1"/>
     <col min="4" max="5" width="9" style="5" customWidth="1"/>
-    <col min="6" max="7" width="37.875" style="3" customWidth="1"/>
-    <col min="8" max="10" width="14.125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="45.125" style="3" customWidth="1"/>
+    <col min="6" max="7" width="37.83203125" style="3" customWidth="1"/>
+    <col min="8" max="10" width="14.08203125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="45.08203125" style="3" customWidth="1"/>
     <col min="12" max="14" width="9" style="3"/>
-    <col min="15" max="15" width="3.125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="3.08203125" style="3" customWidth="1"/>
     <col min="16" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -4940,7 +4919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="19.5" thickBot="1">
+    <row r="3" spans="1:12" ht="18.5" thickBot="1">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -4963,7 +4942,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="94.5" thickBot="1">
+    <row r="4" spans="1:12" ht="90.5" thickBot="1">
       <c r="C4" s="7" t="s">
         <v>8</v>
       </c>
@@ -5115,7 +5094,7 @@
       <c r="J9" s="23"/>
       <c r="K9" s="24"/>
     </row>
-    <row r="10" spans="1:12" ht="19.5" thickBot="1">
+    <row r="10" spans="1:12" ht="18.5" thickBot="1">
       <c r="A10" s="137"/>
       <c r="B10" s="138"/>
       <c r="C10" s="25" t="str">
@@ -5431,7 +5410,7 @@
       <c r="J23" s="23"/>
       <c r="K23" s="33"/>
     </row>
-    <row r="24" spans="1:11" ht="19.5" thickBot="1">
+    <row r="24" spans="1:11" ht="18.5" thickBot="1">
       <c r="A24" s="150"/>
       <c r="B24" s="147"/>
       <c r="C24" s="25" t="str">
@@ -6007,7 +5986,7 @@
       <c r="K48" s="41"/>
       <c r="N48" s="37"/>
     </row>
-    <row r="49" spans="1:14" ht="19.5" thickBot="1">
+    <row r="49" spans="1:14" ht="18.5" thickBot="1">
       <c r="A49" s="141"/>
       <c r="B49" s="138"/>
       <c r="C49" s="25" t="str">
@@ -6030,7 +6009,7 @@
       <c r="K49" s="2"/>
       <c r="N49" s="37"/>
     </row>
-    <row r="50" spans="1:14" ht="19.5">
+    <row r="50" spans="1:14" ht="20">
       <c r="G50" s="42"/>
     </row>
   </sheetData>
@@ -6045,34 +6024,34 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="K5:K10">
-    <cfRule type="expression" dxfId="13" priority="17">
+    <cfRule type="expression" dxfId="15" priority="17">
       <formula>#REF!=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="18">
+    <cfRule type="expression" dxfId="14" priority="18">
       <formula>#REF!=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28">
-    <cfRule type="expression" dxfId="11" priority="5">
+    <cfRule type="expression" dxfId="13" priority="5">
       <formula>#REF!=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="6">
+    <cfRule type="expression" dxfId="12" priority="6">
       <formula>#REF!=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>#REF!=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>#REF!=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38:K49">
-    <cfRule type="expression" dxfId="7" priority="3">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>#REF!=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>#REF!=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6093,15 +6072,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16B3DC52-1465-48EE-B128-D5659D10F49E}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="16.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="33.125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="9.375" style="3" customWidth="1"/>
-    <col min="5" max="6" width="33.125" style="3" customWidth="1"/>
-    <col min="7" max="8" width="13.125" style="3" customWidth="1"/>
-    <col min="9" max="11" width="33.125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="44.125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="16.08203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="33.08203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" style="3" customWidth="1"/>
+    <col min="5" max="6" width="33.08203125" style="3" customWidth="1"/>
+    <col min="7" max="8" width="13.08203125" style="3" customWidth="1"/>
+    <col min="9" max="11" width="33.08203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="44.08203125" style="3" customWidth="1"/>
     <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -6134,7 +6113,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="112.5">
+    <row r="2" spans="1:11" ht="108">
       <c r="B2" s="43" t="s">
         <v>135</v>
       </c>
@@ -6166,7 +6145,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="19.5">
+    <row r="3" spans="1:11" ht="20">
       <c r="A3" s="152" t="s">
         <v>140</v>
       </c>
@@ -6191,7 +6170,7 @@
       <c r="J3" s="50"/>
       <c r="K3" s="23"/>
     </row>
-    <row r="4" spans="1:11" ht="19.5">
+    <row r="4" spans="1:11" ht="20">
       <c r="A4" s="153"/>
       <c r="B4" s="48" t="s">
         <v>143</v>
@@ -6214,7 +6193,7 @@
       <c r="J4" s="50"/>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" spans="1:11" ht="19.5">
+    <row r="5" spans="1:11" ht="20">
       <c r="A5" s="153"/>
       <c r="B5" s="48" t="s">
         <v>145</v>
@@ -6237,7 +6216,7 @@
       <c r="J5" s="50"/>
       <c r="K5" s="23"/>
     </row>
-    <row r="6" spans="1:11" ht="19.5">
+    <row r="6" spans="1:11" ht="20">
       <c r="A6" s="153"/>
       <c r="B6" s="48" t="s">
         <v>148</v>
@@ -6260,7 +6239,7 @@
       <c r="J6" s="50"/>
       <c r="K6" s="23"/>
     </row>
-    <row r="7" spans="1:11" ht="19.5">
+    <row r="7" spans="1:11" ht="20">
       <c r="A7" s="153"/>
       <c r="B7" s="48" t="s">
         <v>151</v>
@@ -6283,7 +6262,7 @@
       <c r="J7" s="50"/>
       <c r="K7" s="23"/>
     </row>
-    <row r="8" spans="1:11" ht="19.5">
+    <row r="8" spans="1:11" ht="20">
       <c r="A8" s="153"/>
       <c r="B8" s="48" t="s">
         <v>154</v>
@@ -6306,7 +6285,7 @@
       <c r="J8" s="50"/>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" spans="1:11" ht="19.5">
+    <row r="9" spans="1:11" ht="20">
       <c r="A9" s="153"/>
       <c r="B9" s="48" t="s">
         <v>157</v>
@@ -6329,7 +6308,7 @@
       <c r="J9" s="50"/>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" spans="1:11" ht="19.5">
+    <row r="10" spans="1:11" ht="20">
       <c r="A10" s="153"/>
       <c r="B10" s="48" t="s">
         <v>160</v>
@@ -6354,7 +6333,7 @@
       <c r="J10" s="50"/>
       <c r="K10" s="23"/>
     </row>
-    <row r="11" spans="1:11" ht="19.5">
+    <row r="11" spans="1:11" ht="20">
       <c r="A11" s="153"/>
       <c r="B11" s="48" t="s">
         <v>164</v>
@@ -6377,7 +6356,7 @@
       <c r="J11" s="50"/>
       <c r="K11" s="23"/>
     </row>
-    <row r="12" spans="1:11" ht="19.5">
+    <row r="12" spans="1:11" ht="20">
       <c r="A12" s="153"/>
       <c r="B12" s="48" t="s">
         <v>167</v>
@@ -6400,7 +6379,7 @@
       <c r="J12" s="50"/>
       <c r="K12" s="23"/>
     </row>
-    <row r="13" spans="1:11" ht="19.5">
+    <row r="13" spans="1:11" ht="20">
       <c r="A13" s="153"/>
       <c r="B13" s="48" t="s">
         <v>170</v>
@@ -6423,7 +6402,7 @@
       <c r="J13" s="53"/>
       <c r="K13" s="52"/>
     </row>
-    <row r="14" spans="1:11" ht="19.5">
+    <row r="14" spans="1:11" ht="20">
       <c r="A14" s="153"/>
       <c r="B14" s="54" t="s">
         <v>173</v>
@@ -6446,7 +6425,7 @@
       <c r="J14" s="53"/>
       <c r="K14" s="52"/>
     </row>
-    <row r="15" spans="1:11" ht="19.5">
+    <row r="15" spans="1:11" ht="20">
       <c r="A15" s="153"/>
       <c r="B15" s="48" t="s">
         <v>176</v>
@@ -6469,7 +6448,7 @@
       <c r="J15" s="50"/>
       <c r="K15" s="23"/>
     </row>
-    <row r="16" spans="1:11" ht="19.5">
+    <row r="16" spans="1:11" ht="20">
       <c r="A16" s="153"/>
       <c r="B16" s="48" t="s">
         <v>179</v>
@@ -6492,7 +6471,7 @@
       <c r="J16" s="50"/>
       <c r="K16" s="23"/>
     </row>
-    <row r="17" spans="1:12" ht="19.5">
+    <row r="17" spans="1:12" ht="20">
       <c r="A17" s="153"/>
       <c r="B17" s="48" t="s">
         <v>182</v>
@@ -6515,7 +6494,7 @@
       <c r="J17" s="50"/>
       <c r="K17" s="23"/>
     </row>
-    <row r="18" spans="1:12" ht="19.5">
+    <row r="18" spans="1:12" ht="20">
       <c r="A18" s="153"/>
       <c r="B18" s="48" t="s">
         <v>185</v>
@@ -6538,7 +6517,7 @@
       <c r="J18" s="50"/>
       <c r="K18" s="23"/>
     </row>
-    <row r="19" spans="1:12" ht="19.5">
+    <row r="19" spans="1:12" ht="20">
       <c r="A19" s="153"/>
       <c r="B19" s="48" t="s">
         <v>188</v>
@@ -6561,7 +6540,7 @@
       <c r="J19" s="50"/>
       <c r="K19" s="21"/>
     </row>
-    <row r="20" spans="1:12" ht="19.5">
+    <row r="20" spans="1:12" ht="20">
       <c r="A20" s="153"/>
       <c r="B20" s="48" t="s">
         <v>191</v>
@@ -6584,7 +6563,7 @@
       <c r="J20" s="50"/>
       <c r="K20" s="21"/>
     </row>
-    <row r="21" spans="1:12" ht="19.5">
+    <row r="21" spans="1:12" ht="20">
       <c r="A21" s="153"/>
       <c r="B21" s="48" t="s">
         <v>194</v>
@@ -6607,7 +6586,7 @@
       <c r="J21" s="50"/>
       <c r="K21" s="21"/>
     </row>
-    <row r="22" spans="1:12" ht="19.5">
+    <row r="22" spans="1:12" ht="20">
       <c r="A22" s="153"/>
       <c r="B22" s="48" t="s">
         <v>197</v>
@@ -6632,7 +6611,7 @@
       <c r="J22" s="50"/>
       <c r="K22" s="21"/>
     </row>
-    <row r="23" spans="1:12" ht="19.5">
+    <row r="23" spans="1:12" ht="20">
       <c r="A23" s="153"/>
       <c r="B23" s="48" t="s">
         <v>202</v>
@@ -6655,7 +6634,7 @@
       <c r="J23" s="50"/>
       <c r="K23" s="23"/>
     </row>
-    <row r="24" spans="1:12" ht="19.5">
+    <row r="24" spans="1:12" ht="20">
       <c r="A24" s="153"/>
       <c r="B24" s="48" t="s">
         <v>205</v>
@@ -6678,7 +6657,7 @@
       <c r="J24" s="50"/>
       <c r="K24" s="23"/>
     </row>
-    <row r="25" spans="1:12" ht="19.5">
+    <row r="25" spans="1:12" ht="20">
       <c r="A25" s="153"/>
       <c r="B25" s="48" t="s">
         <v>208</v>
@@ -6704,7 +6683,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="19.5">
+    <row r="26" spans="1:12" ht="20">
       <c r="A26" s="153"/>
       <c r="B26" s="48" t="s">
         <v>212</v>
@@ -6727,7 +6706,7 @@
       <c r="J26" s="50"/>
       <c r="K26" s="23"/>
     </row>
-    <row r="27" spans="1:12" ht="19.5">
+    <row r="27" spans="1:12" ht="20">
       <c r="A27" s="153"/>
       <c r="B27" s="48" t="s">
         <v>215</v>
@@ -6757,7 +6736,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="19.5">
+    <row r="28" spans="1:12" ht="20">
       <c r="A28" s="153"/>
       <c r="B28" s="48" t="s">
         <v>221</v>
@@ -6785,7 +6764,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="19.5">
+    <row r="29" spans="1:12" ht="20">
       <c r="A29" s="153"/>
       <c r="B29" s="48" t="s">
         <v>225</v>
@@ -6808,7 +6787,7 @@
       <c r="J29" s="50"/>
       <c r="K29" s="23"/>
     </row>
-    <row r="30" spans="1:12" ht="19.5">
+    <row r="30" spans="1:12" ht="20">
       <c r="A30" s="153"/>
       <c r="B30" s="48" t="s">
         <v>228</v>
@@ -6831,7 +6810,7 @@
       <c r="J30" s="50"/>
       <c r="K30" s="23"/>
     </row>
-    <row r="31" spans="1:12" ht="19.5">
+    <row r="31" spans="1:12" ht="20">
       <c r="A31" s="153"/>
       <c r="B31" s="48" t="s">
         <v>231</v>
@@ -6854,7 +6833,7 @@
       <c r="J31" s="50"/>
       <c r="K31" s="23"/>
     </row>
-    <row r="32" spans="1:12" ht="19.5">
+    <row r="32" spans="1:12" ht="20">
       <c r="A32" s="153"/>
       <c r="B32" s="48" t="s">
         <v>234</v>
@@ -6877,7 +6856,7 @@
       <c r="J32" s="50"/>
       <c r="K32" s="23"/>
     </row>
-    <row r="33" spans="1:12" ht="19.5">
+    <row r="33" spans="1:12" ht="20">
       <c r="A33" s="153"/>
       <c r="B33" s="48" t="s">
         <v>237</v>
@@ -6900,7 +6879,7 @@
       <c r="J33" s="50"/>
       <c r="K33" s="23"/>
     </row>
-    <row r="34" spans="1:12" ht="19.5">
+    <row r="34" spans="1:12" ht="20">
       <c r="A34" s="153"/>
       <c r="B34" s="48" t="s">
         <v>240</v>
@@ -6923,7 +6902,7 @@
       <c r="J34" s="50"/>
       <c r="K34" s="23"/>
     </row>
-    <row r="35" spans="1:12" ht="19.5">
+    <row r="35" spans="1:12" ht="20">
       <c r="A35" s="153"/>
       <c r="B35" s="48" t="s">
         <v>243</v>
@@ -6946,7 +6925,7 @@
       <c r="J35" s="50"/>
       <c r="K35" s="23"/>
     </row>
-    <row r="36" spans="1:12" ht="19.5">
+    <row r="36" spans="1:12" ht="20">
       <c r="A36" s="153"/>
       <c r="B36" s="48" t="s">
         <v>246</v>
@@ -6971,7 +6950,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="19.5">
+    <row r="37" spans="1:12" ht="20">
       <c r="A37" s="153"/>
       <c r="B37" s="48" t="s">
         <v>252</v>
@@ -6996,7 +6975,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="19.5">
+    <row r="38" spans="1:12" ht="20">
       <c r="A38" s="153"/>
       <c r="B38" s="48" t="s">
         <v>256</v>
@@ -7021,7 +7000,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="37.5">
+    <row r="39" spans="1:12" ht="36">
       <c r="A39" s="154"/>
       <c r="B39" s="48"/>
       <c r="C39" s="19"/>
@@ -7051,10 +7030,10 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="J3:J39">
-    <cfRule type="expression" dxfId="5" priority="13">
+    <cfRule type="expression" dxfId="7" priority="13">
       <formula>#REF!=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="15">
+    <cfRule type="expression" dxfId="6" priority="15">
       <formula>#REF!=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7072,19 +7051,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E016AB2A-BE75-4524-8D89-1C70CA20E688}">
   <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="44.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="25.625" customWidth="1"/>
-    <col min="5" max="5" width="25.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="25.625" customWidth="1"/>
-    <col min="8" max="8" width="19.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.875" customWidth="1"/>
-    <col min="10" max="10" width="25.625" customWidth="1"/>
-    <col min="11" max="11" width="19.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.875" customWidth="1"/>
-    <col min="13" max="13" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="25.58203125" customWidth="1"/>
+    <col min="5" max="5" width="25.58203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="25.58203125" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.83203125" customWidth="1"/>
+    <col min="10" max="10" width="25.58203125" customWidth="1"/>
+    <col min="11" max="11" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.83203125" customWidth="1"/>
+    <col min="13" max="13" width="21.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -7185,17 +7164,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D47BE4CE-9366-40E8-8DF1-D4B9CF138C00}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="2" width="19" style="3" customWidth="1"/>
-    <col min="3" max="3" width="50.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="50.83203125" style="3" customWidth="1"/>
     <col min="4" max="5" width="9" style="5" customWidth="1"/>
-    <col min="6" max="7" width="37.875" style="3" customWidth="1"/>
-    <col min="8" max="9" width="14.125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="14.125" style="3" hidden="1" customWidth="1"/>
-    <col min="11" max="12" width="45.125" style="3" customWidth="1"/>
+    <col min="6" max="7" width="37.83203125" style="3" customWidth="1"/>
+    <col min="8" max="9" width="14.08203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="14.08203125" style="3" hidden="1" customWidth="1"/>
+    <col min="11" max="12" width="45.08203125" style="3" customWidth="1"/>
     <col min="13" max="14" width="9" style="3"/>
-    <col min="15" max="15" width="3.125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="3.08203125" style="3" customWidth="1"/>
     <col min="16" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -7204,7 +7183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="19.5" thickBot="1">
+    <row r="3" spans="1:12" ht="18.5" thickBot="1">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -7228,7 +7207,7 @@
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="1:12" ht="94.5" thickBot="1">
+    <row r="4" spans="1:12" ht="90.5" thickBot="1">
       <c r="A4" s="155"/>
       <c r="B4" s="155"/>
       <c r="C4" s="94" t="s">
@@ -7362,7 +7341,7 @@
       <c r="K8" s="24"/>
       <c r="L8" s="24"/>
     </row>
-    <row r="9" spans="1:12" ht="19.5" thickBot="1">
+    <row r="9" spans="1:12" ht="18.5" thickBot="1">
       <c r="A9" s="160"/>
       <c r="B9" s="161"/>
       <c r="C9" s="91" t="str">
@@ -7389,15 +7368,15 @@
       <c r="A10" s="129"/>
       <c r="B10" s="129"/>
       <c r="C10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D10" s="31"/>
       <c r="E10" s="31"/>
       <c r="F10" s="32" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G10" s="32" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H10" s="21" t="s">
         <v>21</v>
@@ -7411,18 +7390,18 @@
       <c r="A11" s="130"/>
       <c r="B11" s="130"/>
       <c r="C11" s="92" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D11" s="31"/>
       <c r="E11" s="31"/>
       <c r="F11" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="G11" s="32" t="s">
         <v>305</v>
       </c>
-      <c r="G11" s="32" t="s">
-        <v>304</v>
-      </c>
       <c r="H11" s="21" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I11" s="23"/>
       <c r="J11" s="23"/>
@@ -7437,15 +7416,15 @@
         <v>273</v>
       </c>
       <c r="C12" s="92" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D12" s="22"/>
       <c r="E12" s="22"/>
       <c r="F12" s="32" t="s">
+        <v>309</v>
+      </c>
+      <c r="G12" s="32" t="s">
         <v>308</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>307</v>
       </c>
       <c r="H12" s="21" t="s">
         <v>21</v>
@@ -7459,15 +7438,15 @@
       <c r="A13" s="130"/>
       <c r="B13" s="130"/>
       <c r="C13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D13" s="31"/>
       <c r="E13" s="31"/>
       <c r="F13" s="32" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G13" s="32" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H13" s="21" t="s">
         <v>21</v>
@@ -7481,15 +7460,15 @@
       <c r="A14" s="131"/>
       <c r="B14" s="131"/>
       <c r="C14" s="92" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="22"/>
       <c r="F14" s="32" t="s">
+        <v>314</v>
+      </c>
+      <c r="G14" s="32" t="s">
         <v>313</v>
-      </c>
-      <c r="G14" s="32" t="s">
-        <v>312</v>
       </c>
       <c r="H14" s="21" t="s">
         <v>21</v>
@@ -7519,7 +7498,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="4:7" ht="19.5">
+    <row r="20" spans="4:7" ht="20">
       <c r="G20" s="42"/>
     </row>
     <row r="27" spans="4:7" ht="18.75" customHeight="1"/>
@@ -7530,7 +7509,15 @@
     <mergeCell ref="A5:B9"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="K5:L9 K12:L12">
+  <conditionalFormatting sqref="K5:K9">
+    <cfRule type="expression" dxfId="5" priority="13">
+      <formula>#REF!=1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="14">
+      <formula>#REF!=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L5:L9 K12:L12">
     <cfRule type="expression" dxfId="3" priority="7">
       <formula>#REF!=1</formula>
     </cfRule>
@@ -7551,19 +7538,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A67A099-D1D9-47C6-9CCA-1E0707904294}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="16.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="33.125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="33.08203125" style="3" customWidth="1"/>
     <col min="4" max="4" width="9.5" style="3" customWidth="1"/>
-    <col min="5" max="5" width="33.125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="32.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="5.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33.125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="43.125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="44.375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="33.08203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="32.08203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.08203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="5.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.08203125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="43.08203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="44.33203125" style="3" customWidth="1"/>
     <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -7596,7 +7583,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="93.75">
+    <row r="2" spans="1:11" ht="90">
       <c r="A2" s="43" t="s">
         <v>275</v>
       </c>
@@ -7631,145 +7618,145 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="19.5">
+    <row r="3" spans="1:11" ht="20">
       <c r="A3" s="93" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B3" s="48"/>
       <c r="C3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G3" s="23" t="s">
         <v>200</v>
       </c>
       <c r="H3" s="126" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I3" s="23"/>
       <c r="J3" s="50"/>
       <c r="K3" s="23" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="19.5">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="20">
       <c r="A4" s="93"/>
       <c r="B4" s="48"/>
       <c r="C4" s="125" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G4" s="23" t="s">
         <v>200</v>
       </c>
       <c r="H4" s="126" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I4" s="23"/>
       <c r="J4" s="50"/>
       <c r="K4" s="23" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="18" customHeight="1">
       <c r="A5" s="93"/>
       <c r="B5" s="23"/>
       <c r="C5" s="23" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="23" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G5" s="23" t="s">
         <v>200</v>
       </c>
       <c r="H5" s="127" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I5" s="23"/>
       <c r="J5" s="50"/>
       <c r="K5" s="23" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="19.5">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="20">
       <c r="A6" s="93"/>
       <c r="B6" s="48"/>
       <c r="C6" s="125" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D6" s="23"/>
       <c r="E6" s="23" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G6" s="23" t="s">
         <v>200</v>
       </c>
       <c r="H6" s="126" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="50"/>
       <c r="K6" s="23" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="19.5">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="20">
       <c r="A7" s="93"/>
       <c r="B7" s="48"/>
       <c r="C7" s="125" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D7" s="23"/>
       <c r="E7" s="23" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G7" s="23" t="s">
         <v>200</v>
       </c>
       <c r="H7" s="126" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="50"/>
       <c r="K7" s="23" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="19.5">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="20">
       <c r="A8" s="93"/>
       <c r="B8" s="48"/>
       <c r="C8" s="125" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D8" s="23"/>
       <c r="E8" s="23" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G8" s="23" t="s">
         <v>27</v>
@@ -7778,46 +7765,46 @@
       <c r="I8" s="23"/>
       <c r="J8" s="50"/>
       <c r="K8" s="23" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="19.5">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="20">
       <c r="A9" s="93"/>
       <c r="B9" s="105"/>
       <c r="C9" s="125" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D9" s="38"/>
       <c r="E9" s="38" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G9" s="38" t="s">
         <v>249</v>
       </c>
       <c r="H9" s="128" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I9" s="38"/>
       <c r="J9" s="106"/>
       <c r="K9" s="23" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="19.5">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="20">
       <c r="A10" s="104"/>
       <c r="B10" s="48"/>
       <c r="C10" s="125" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D10" s="23"/>
       <c r="E10" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="F10" s="23" t="s">
         <v>339</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>338</v>
       </c>
       <c r="G10" s="23" t="s">
         <v>249</v>
@@ -7826,7 +7813,7 @@
       <c r="I10" s="23"/>
       <c r="J10" s="50"/>
       <c r="K10" s="23" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -7847,17 +7834,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2893B45F-5141-4774-9CD5-206CB136A49F}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="20.625" customWidth="1"/>
-    <col min="2" max="2" width="5.125" customWidth="1"/>
-    <col min="3" max="3" width="25.125" customWidth="1"/>
-    <col min="4" max="4" width="49.875" customWidth="1"/>
+    <col min="1" max="1" width="20.58203125" customWidth="1"/>
+    <col min="2" max="2" width="5.08203125" customWidth="1"/>
+    <col min="3" max="3" width="25.08203125" customWidth="1"/>
+    <col min="4" max="4" width="49.83203125" customWidth="1"/>
     <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="41.125" customWidth="1"/>
+    <col min="6" max="6" width="41.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.5">
+    <row r="1" spans="1:6" ht="20">
       <c r="A1" s="107" t="s">
         <v>277</v>
       </c>
@@ -7881,12 +7868,12 @@
         <v>291</v>
       </c>
       <c r="C2" s="164" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D2" s="165"/>
       <c r="E2" s="166"/>
       <c r="F2" s="119" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -7918,7 +7905,7 @@
         <v>290</v>
       </c>
       <c r="D4" s="114" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E4" s="114" t="s">
         <v>287</v>
@@ -7931,27 +7918,27 @@
         <v>18</v>
       </c>
       <c r="C5" s="115" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D5" s="114" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="115" t="s">
         <v>298</v>
       </c>
-      <c r="E5" s="115" t="s">
-        <v>297</v>
-      </c>
       <c r="F5" s="115"/>
     </row>
-    <row r="6" spans="1:6" ht="36.6" customHeight="1">
+    <row r="6" spans="1:6" ht="36.5" customHeight="1">
       <c r="A6" s="122"/>
       <c r="B6" s="124"/>
       <c r="C6" s="115" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D6" s="114" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E6" s="120" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F6" s="115"/>
     </row>
@@ -7974,10 +7961,10 @@
   <cols>
     <col min="1" max="1" width="9" style="74"/>
     <col min="2" max="3" width="14" style="74" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.625" style="74" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="97.625" style="74" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.125" style="75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="64.375" style="75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.58203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="97.58203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.08203125" style="75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="64.33203125" style="75" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="74"/>
   </cols>
   <sheetData>
@@ -8017,7 +8004,7 @@
         <v>45651</v>
       </c>
       <c r="C5" s="69" t="s">
-        <v>341</v>
+        <v>292</v>
       </c>
       <c r="D5" s="69"/>
       <c r="E5" s="70" t="s">
@@ -8410,6 +8397,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e1b7570-88a0-44ee-ab1c-d900d3a9ef2f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="69806635-1477-418f-8922-2a2d0bbc39e0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101000ED353C60105F34DABBBF603193D9FD7" ma:contentTypeVersion="8" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ff96f1b83903b6ca69e21ae72ce65d29">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7e1b7570-88a0-44ee-ab1c-d900d3a9ef2f" xmlns:ns3="69806635-1477-418f-8922-2a2d0bbc39e0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dd34249053b4960b9f5dac26d98b1ad9" ns2:_="" ns3:_="">
     <xsd:import namespace="7e1b7570-88a0-44ee-ab1c-d900d3a9ef2f"/>
@@ -8586,27 +8593,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e1b7570-88a0-44ee-ab1c-d900d3a9ef2f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="69806635-1477-418f-8922-2a2d0bbc39e0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F1080EF-91B6-417D-A249-69224D257C51}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB043C42-5D59-4A30-92A0-5EA74B604AF5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7e1b7570-88a0-44ee-ab1c-d900d3a9ef2f"/>
+    <ds:schemaRef ds:uri="69806635-1477-418f-8922-2a2d0bbc39e0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C04DD24-2E45-4DC0-B69F-E7DC5E36A116}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8623,23 +8629,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB043C42-5D59-4A30-92A0-5EA74B604AF5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7e1b7570-88a0-44ee-ab1c-d900d3a9ef2f"/>
-    <ds:schemaRef ds:uri="69806635-1477-418f-8922-2a2d0bbc39e0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F1080EF-91B6-417D-A249-69224D257C51}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>